--- a/data/EMEA_Sales_Ops_Toolkit.xlsx
+++ b/data/EMEA_Sales_Ops_Toolkit.xlsx
@@ -30072,7 +30072,7 @@
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
-          <t>Pipeline (USD)</t>
+          <t>Pipeline (EUR)</t>
         </is>
       </c>
       <c r="J1" s="3" t="inlineStr">
